--- a/Design Files/BLDC-Board-v1.0/BOM/eSpark-BOM-BLDC-Board-v1.0.xlsx
+++ b/Design Files/BLDC-Board-v1.0/BOM/eSpark-BOM-BLDC-Board-v1.0.xlsx
@@ -12,14 +12,14 @@
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15840"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="5 Boards" sheetId="1" r:id="rId1"/>
   </sheets>
   <calcPr calcId="162913"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="987" uniqueCount="554">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1017" uniqueCount="567">
   <si>
     <t>Component list</t>
   </si>
@@ -1681,6 +1681,45 @@
   </si>
   <si>
     <t>C144873</t>
+  </si>
+  <si>
+    <t>Peripheral</t>
+  </si>
+  <si>
+    <t>32V Blade fuse 15A Automotive Fuses ROHS</t>
+  </si>
+  <si>
+    <t>0287015.PXCN</t>
+  </si>
+  <si>
+    <t>Jumper</t>
+  </si>
+  <si>
+    <t>P=2.54mm Shunts, Jumpers ROHS</t>
+  </si>
+  <si>
+    <t>X2541-A1NIB</t>
+  </si>
+  <si>
+    <t>Ethernet Cable</t>
+  </si>
+  <si>
+    <t>Cat6 Gigabit Ethernet Cable 1m Cable/ModularCable</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Littelfuse </t>
+  </si>
+  <si>
+    <t xml:space="preserve">UGREEN </t>
+  </si>
+  <si>
+    <t>C2938578</t>
+  </si>
+  <si>
+    <t>C3015021</t>
+  </si>
+  <si>
+    <t>C142684</t>
   </si>
 </sst>
 </file>
@@ -2160,17 +2199,6 @@
     <xf numFmtId="0" fontId="15" fillId="2" borderId="7" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="top"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="top"/>
-      <protection locked="0"/>
-    </xf>
     <xf numFmtId="166" fontId="15" fillId="2" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -2200,6 +2228,17 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="top"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="top"/>
+      <protection locked="0"/>
+    </xf>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -2488,7 +2527,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet1"/>
-  <dimension ref="A1:Y116"/>
+  <dimension ref="A1:Y119"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="3.140625" style="10" customWidth="1"/>
@@ -2524,14 +2563,14 @@
       <c r="H1" s="2"/>
       <c r="I1" s="2"/>
       <c r="J1" s="2"/>
-      <c r="K1" s="51"/>
-      <c r="L1" s="51"/>
-      <c r="M1" s="51"/>
-      <c r="N1" s="51"/>
-      <c r="O1" s="51"/>
-      <c r="P1" s="51"/>
-      <c r="Q1" s="51"/>
-      <c r="R1" s="51"/>
+      <c r="K1" s="62"/>
+      <c r="L1" s="62"/>
+      <c r="M1" s="62"/>
+      <c r="N1" s="62"/>
+      <c r="O1" s="62"/>
+      <c r="P1" s="62"/>
+      <c r="Q1" s="62"/>
+      <c r="R1" s="62"/>
     </row>
     <row r="2" spans="1:18" ht="32.25" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A2" s="1"/>
@@ -2744,7 +2783,7 @@
       <c r="P8" s="20">
         <v>2.0999999999999999E-3</v>
       </c>
-      <c r="Q8" s="54">
+      <c r="Q8" s="51">
         <f>P8*N8</f>
         <v>0.21</v>
       </c>
@@ -3631,60 +3670,60 @@
       </c>
       <c r="R24" s="19"/>
     </row>
-    <row r="25" spans="1:25" s="64" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A25" s="55"/>
+    <row r="25" spans="1:25" s="61" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A25" s="52"/>
       <c r="B25" s="16">
         <f t="shared" si="1"/>
         <v>18</v>
       </c>
-      <c r="C25" s="56" t="s">
+      <c r="C25" s="53" t="s">
         <v>6</v>
       </c>
-      <c r="D25" s="57" t="s">
+      <c r="D25" s="54" t="s">
         <v>538</v>
       </c>
-      <c r="E25" s="57" t="s">
+      <c r="E25" s="54" t="s">
         <v>123</v>
       </c>
-      <c r="F25" s="57" t="s">
+      <c r="F25" s="54" t="s">
         <v>215</v>
       </c>
-      <c r="G25" s="57" t="s">
+      <c r="G25" s="54" t="s">
         <v>263</v>
       </c>
-      <c r="H25" s="57" t="s">
+      <c r="H25" s="54" t="s">
         <v>343</v>
       </c>
-      <c r="I25" s="58" t="s">
-        <v>535</v>
-      </c>
-      <c r="J25" s="57" t="s">
+      <c r="I25" s="55" t="s">
+        <v>535</v>
+      </c>
+      <c r="J25" s="54" t="s">
         <v>384</v>
       </c>
-      <c r="K25" s="59" t="s">
+      <c r="K25" s="56" t="s">
         <v>468</v>
       </c>
-      <c r="L25" s="57">
+      <c r="L25" s="54">
         <v>8</v>
       </c>
-      <c r="M25" s="57">
+      <c r="M25" s="54">
         <f>L25*5</f>
         <v>40</v>
       </c>
-      <c r="N25" s="60">
+      <c r="N25" s="57">
         <v>100</v>
       </c>
-      <c r="O25" s="61" t="s">
-        <v>523</v>
-      </c>
-      <c r="P25" s="62">
+      <c r="O25" s="58" t="s">
+        <v>523</v>
+      </c>
+      <c r="P25" s="59">
         <v>2.0999999999999999E-3</v>
       </c>
-      <c r="Q25" s="63">
+      <c r="Q25" s="60">
         <f>P25*N25</f>
         <v>0.21</v>
       </c>
-      <c r="R25" s="57"/>
+      <c r="R25" s="54"/>
       <c r="T25"/>
       <c r="U25"/>
       <c r="V25"/>
@@ -4963,7 +5002,9 @@
         <f t="shared" si="1"/>
         <v>42</v>
       </c>
-      <c r="C49" s="21"/>
+      <c r="C49" s="21" t="s">
+        <v>17</v>
+      </c>
       <c r="D49" s="14" t="s">
         <v>70</v>
       </c>
@@ -6279,7 +6320,7 @@
     <row r="73" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A73" s="1"/>
       <c r="B73" s="16">
-        <f t="shared" ref="B73:B102" si="62">ROW(B73) - ROW($B$7)</f>
+        <f t="shared" ref="B73:B105" si="62">ROW(B73) - ROW($B$7)</f>
         <v>66</v>
       </c>
       <c r="C73" s="21" t="s">
@@ -7873,7 +7914,7 @@
       </c>
       <c r="R101" s="19"/>
     </row>
-    <row r="102" spans="1:18" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="102" spans="1:18" ht="24" x14ac:dyDescent="0.25">
       <c r="A102" s="1"/>
       <c r="B102" s="16">
         <f t="shared" si="62"/>
@@ -7928,64 +7969,229 @@
       </c>
       <c r="R102" s="14"/>
     </row>
-    <row r="103" spans="1:18" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="103" spans="1:18" ht="24" x14ac:dyDescent="0.25">
       <c r="A103" s="1"/>
-      <c r="B103" s="1"/>
-      <c r="C103" s="1"/>
-      <c r="D103" s="1"/>
-      <c r="E103" s="1"/>
-      <c r="F103" s="1"/>
-      <c r="G103" s="1"/>
-      <c r="H103" s="1"/>
-      <c r="I103" s="1"/>
-      <c r="J103" s="1"/>
-      <c r="K103" s="1"/>
-      <c r="L103" s="1"/>
-      <c r="M103" s="1"/>
-      <c r="N103" s="52" t="s">
+      <c r="B103" s="16">
+        <f t="shared" si="62"/>
+        <v>96</v>
+      </c>
+      <c r="C103" s="21" t="s">
+        <v>554</v>
+      </c>
+      <c r="D103" s="14" t="s">
+        <v>10</v>
+      </c>
+      <c r="E103" s="41" t="s">
+        <v>555</v>
+      </c>
+      <c r="F103" s="14" t="s">
+        <v>531</v>
+      </c>
+      <c r="G103" s="41" t="s">
+        <v>556</v>
+      </c>
+      <c r="H103" s="14" t="s">
+        <v>562</v>
+      </c>
+      <c r="I103" s="50" t="s">
+        <v>535</v>
+      </c>
+      <c r="J103" s="14" t="s">
+        <v>566</v>
+      </c>
+      <c r="K103" s="41" t="s">
+        <v>514</v>
+      </c>
+      <c r="L103" s="14">
+        <v>1</v>
+      </c>
+      <c r="M103" s="14">
+        <f>L103*5</f>
+        <v>5</v>
+      </c>
+      <c r="N103" s="14">
+        <v>6</v>
+      </c>
+      <c r="O103" s="48" t="s">
+        <v>523</v>
+      </c>
+      <c r="P103" s="15">
+        <v>0.08</v>
+      </c>
+      <c r="Q103" s="15">
+        <f t="shared" ref="Q103:Q105" si="91">P103*N103</f>
+        <v>0.48</v>
+      </c>
+      <c r="R103" s="14"/>
+    </row>
+    <row r="104" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A104" s="1"/>
+      <c r="B104" s="16">
+        <f t="shared" si="62"/>
+        <v>97</v>
+      </c>
+      <c r="C104" s="21" t="s">
+        <v>554</v>
+      </c>
+      <c r="D104" s="14" t="s">
+        <v>557</v>
+      </c>
+      <c r="E104" s="41" t="s">
+        <v>558</v>
+      </c>
+      <c r="F104" s="14" t="s">
+        <v>531</v>
+      </c>
+      <c r="G104" s="41" t="s">
+        <v>559</v>
+      </c>
+      <c r="H104" s="14" t="s">
+        <v>360</v>
+      </c>
+      <c r="I104" s="50" t="s">
+        <v>535</v>
+      </c>
+      <c r="J104" s="14" t="s">
+        <v>564</v>
+      </c>
+      <c r="K104" s="41" t="s">
+        <v>514</v>
+      </c>
+      <c r="L104" s="14">
+        <v>5</v>
+      </c>
+      <c r="M104" s="14">
+        <f>L104*5</f>
+        <v>25</v>
+      </c>
+      <c r="N104" s="14">
+        <v>40</v>
+      </c>
+      <c r="O104" s="48" t="s">
+        <v>523</v>
+      </c>
+      <c r="P104" s="15">
+        <v>2.01E-2</v>
+      </c>
+      <c r="Q104" s="15">
+        <f t="shared" si="91"/>
+        <v>0.80400000000000005</v>
+      </c>
+      <c r="R104" s="14"/>
+    </row>
+    <row r="105" spans="1:18" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A105" s="1"/>
+      <c r="B105" s="16">
+        <f t="shared" si="62"/>
+        <v>98</v>
+      </c>
+      <c r="C105" s="21" t="s">
+        <v>554</v>
+      </c>
+      <c r="D105" s="14" t="s">
+        <v>560</v>
+      </c>
+      <c r="E105" s="41" t="s">
+        <v>561</v>
+      </c>
+      <c r="F105" s="14" t="s">
+        <v>531</v>
+      </c>
+      <c r="G105" s="41">
+        <v>50173</v>
+      </c>
+      <c r="H105" s="14" t="s">
+        <v>563</v>
+      </c>
+      <c r="I105" s="50" t="s">
+        <v>535</v>
+      </c>
+      <c r="J105" s="14" t="s">
+        <v>565</v>
+      </c>
+      <c r="K105" s="41" t="s">
+        <v>514</v>
+      </c>
+      <c r="L105" s="14">
+        <v>1</v>
+      </c>
+      <c r="M105" s="14">
+        <f>L105*5</f>
+        <v>5</v>
+      </c>
+      <c r="N105" s="14">
+        <v>6</v>
+      </c>
+      <c r="O105" s="48" t="s">
+        <v>523</v>
+      </c>
+      <c r="P105" s="15">
+        <v>1.3977999999999999</v>
+      </c>
+      <c r="Q105" s="15">
+        <f t="shared" si="91"/>
+        <v>8.3867999999999991</v>
+      </c>
+      <c r="R105" s="14"/>
+    </row>
+    <row r="106" spans="1:18" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A106" s="1"/>
+      <c r="B106" s="1"/>
+      <c r="C106" s="1"/>
+      <c r="D106" s="1"/>
+      <c r="E106" s="1"/>
+      <c r="F106" s="1"/>
+      <c r="G106" s="1"/>
+      <c r="H106" s="1"/>
+      <c r="I106" s="1"/>
+      <c r="J106" s="1"/>
+      <c r="K106" s="1"/>
+      <c r="L106" s="1"/>
+      <c r="M106" s="1"/>
+      <c r="N106" s="63" t="s">
         <v>3</v>
       </c>
-      <c r="O103" s="53"/>
-      <c r="P103" s="53"/>
-      <c r="Q103" s="17">
-        <f>SUM(Q8:Q102)</f>
-        <v>272.3574999999999</v>
-      </c>
-      <c r="R103" s="1"/>
-    </row>
-    <row r="104" spans="1:18" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A104" s="1"/>
-      <c r="B104" s="1"/>
-      <c r="C104" s="1"/>
-      <c r="D104" s="1"/>
-      <c r="E104" s="1"/>
-      <c r="F104" s="1"/>
-      <c r="G104" s="1"/>
-      <c r="H104" s="1"/>
-      <c r="I104" s="1"/>
-      <c r="J104" s="1"/>
-      <c r="K104" s="1"/>
-      <c r="L104" s="1"/>
-      <c r="M104" s="1"/>
-      <c r="N104" s="52" t="s">
+      <c r="O106" s="64"/>
+      <c r="P106" s="64"/>
+      <c r="Q106" s="17">
+        <f>SUM(Q8:Q105)</f>
+        <v>282.02829999999989</v>
+      </c>
+      <c r="R106" s="1"/>
+    </row>
+    <row r="107" spans="1:18" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A107" s="1"/>
+      <c r="B107" s="1"/>
+      <c r="C107" s="1"/>
+      <c r="D107" s="1"/>
+      <c r="E107" s="1"/>
+      <c r="F107" s="1"/>
+      <c r="G107" s="1"/>
+      <c r="H107" s="1"/>
+      <c r="I107" s="1"/>
+      <c r="J107" s="1"/>
+      <c r="K107" s="1"/>
+      <c r="L107" s="1"/>
+      <c r="M107" s="1"/>
+      <c r="N107" s="63" t="s">
         <v>4</v>
       </c>
-      <c r="O104" s="53"/>
-      <c r="P104" s="53"/>
-      <c r="Q104" s="18">
-        <f>Q103/5</f>
-        <v>54.471499999999978</v>
-      </c>
-      <c r="R104" s="1"/>
-    </row>
-    <row r="116" spans="13:13" x14ac:dyDescent="0.25">
-      <c r="M116" s="37"/>
+      <c r="O107" s="64"/>
+      <c r="P107" s="64"/>
+      <c r="Q107" s="18">
+        <f>Q106/5</f>
+        <v>56.405659999999976</v>
+      </c>
+      <c r="R107" s="1"/>
+    </row>
+    <row r="119" spans="13:13" x14ac:dyDescent="0.25">
+      <c r="M119" s="37"/>
     </row>
   </sheetData>
   <mergeCells count="3">
     <mergeCell ref="K1:R1"/>
-    <mergeCell ref="N103:P103"/>
-    <mergeCell ref="N104:P104"/>
+    <mergeCell ref="N106:P106"/>
+    <mergeCell ref="N107:P107"/>
   </mergeCells>
   <hyperlinks>
     <hyperlink ref="O10" r:id="rId1"/>
@@ -8079,8 +8285,11 @@
     <hyperlink ref="O25" r:id="rId89"/>
     <hyperlink ref="O36" r:id="rId90"/>
     <hyperlink ref="O99" r:id="rId91"/>
+    <hyperlink ref="O104" r:id="rId92"/>
+    <hyperlink ref="O103" r:id="rId93"/>
+    <hyperlink ref="O105" r:id="rId94"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" r:id="rId92"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId95"/>
 </worksheet>
 </file>